--- a/tiflow/ti-flow-system-diagram/2.0.0-ballot.2/ValueSet-tiflow-operation-outcome-details-vs.xlsx
+++ b/tiflow/ti-flow-system-diagram/2.0.0-ballot.2/ValueSet-tiflow-operation-outcome-details-vs.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="57">
   <si>
     <t>Property</t>
   </si>
@@ -168,12 +168,6 @@
   </si>
   <si>
     <t>MSG_BAD_FORMAT</t>
-  </si>
-  <si>
-    <t>MSG_TIMEOUT</t>
-  </si>
-  <si>
-    <t>MSG_INTERNAL_ERROR</t>
   </si>
   <si>
     <t>MSG_UNKNOWN_TYPE</t>
@@ -567,7 +561,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -644,30 +638,18 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="B11" s="2"/>
+        <v>31</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>31</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>57</v>
-      </c>
-      <c r="B12" s="2"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="2">
         <v>32</v>
       </c>
-      <c r="B14" t="s" s="2">
-        <v>58</v>
+      <c r="B12" t="s" s="2">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
